--- a/progress_tracker.xlsx
+++ b/progress_tracker.xlsx
@@ -490,22 +490,24 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>ANDAMAN AND NICOBAR ISLANDS</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>NORTH AND MIDDLE ANDAMAN</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>☑</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -15726,10 +15728,10 @@
         <v>3</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>182</v>
+        <v>282</v>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
